--- a/output/CS_SFIAFormat/sfiaformat_mapping_cosine_SkillNER_CS.xlsx
+++ b/output/CS_SFIAFormat/sfiaformat_mapping_cosine_SkillNER_CS.xlsx
@@ -480,7 +480,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>0.2025</v>
+        <v>0.3213</v>
       </c>
       <c r="F2" t="n">
         <v>0.3403</v>
@@ -489,7 +489,7 @@
         <v>0.2833</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2083</v>
+        <v>0.3556</v>
       </c>
     </row>
     <row r="3">
@@ -504,10 +504,10 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>0.2194</v>
+        <v>0.2729</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2416</v>
+        <v>0.3183</v>
       </c>
     </row>
     <row r="4">
@@ -519,7 +519,7 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.225</v>
+        <v>0.2493</v>
       </c>
       <c r="E4" t="n">
         <v>0.2545</v>
@@ -528,7 +528,7 @@
         <v>0.2079</v>
       </c>
       <c r="G4" t="n">
-        <v>0.229</v>
+        <v>0.2935</v>
       </c>
       <c r="H4" t="n">
         <v>0.2072</v>
@@ -545,13 +545,13 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>0.2557</v>
+        <v>0.443</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2182</v>
+        <v>0.3984</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2009</v>
+        <v>0.2623</v>
       </c>
     </row>
     <row r="6">
@@ -564,13 +564,13 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>0.3052</v>
+        <v>0.4411</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2197</v>
+        <v>0.4979</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3128</v>
+        <v>0.4211</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -598,13 +598,13 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>0.2427</v>
+        <v>0.4191</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2507</v>
+        <v>0.3785</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2631</v>
+        <v>0.4316</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -651,10 +651,10 @@
         <v>0.3204</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2606</v>
+        <v>0.3978</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2837</v>
+        <v>0.3143</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -687,10 +687,10 @@
         <v>0.2048</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2204</v>
+        <v>0.2406</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2296</v>
+        <v>0.2325</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -702,16 +702,16 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>0.2042</v>
+        <v>0.2263</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2052</v>
+        <v>0.2318</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2176</v>
+        <v>0.2493</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2048</v>
+        <v>0.2374</v>
       </c>
       <c r="G14" t="n">
         <v>0.2068</v>
@@ -729,13 +729,13 @@
         <v>0.4271</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2009</v>
+        <v>0.3758</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2136</v>
+        <v>0.4399</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2068</v>
+        <v>0.4003</v>
       </c>
       <c r="G15" t="n">
         <v>0.4168</v>
@@ -776,7 +776,7 @@
         <v>0.2351</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2419</v>
+        <v>0.2989</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -789,11 +789,11 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.2234</v>
+        <v>0.2413</v>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>0.2356</v>
+        <v>0.264</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -806,22 +806,22 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>0.2104</v>
+        <v>0.517</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2495</v>
+        <v>0.4191</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2128</v>
+        <v>0.4228</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2021</v>
+        <v>0.5533</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2745</v>
+        <v>0.3596</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2247</v>
+        <v>0.4761</v>
       </c>
     </row>
     <row r="20">
@@ -832,22 +832,22 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>0.2345</v>
+        <v>0.3641</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2604</v>
+        <v>0.2904</v>
       </c>
       <c r="E20" t="n">
-        <v>0.213</v>
+        <v>0.3447</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2008</v>
+        <v>0.3889</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2142</v>
+        <v>0.3784</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2242</v>
+        <v>0.4003</v>
       </c>
     </row>
     <row r="21">
@@ -866,7 +866,7 @@
         <v>0.2153</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2018</v>
+        <v>0.3138</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -910,10 +910,10 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>0.2444</v>
+        <v>0.3481</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2054</v>
+        <v>0.4326</v>
       </c>
     </row>
     <row r="25">
@@ -924,22 +924,22 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>0.2254</v>
+        <v>0.5074</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2208</v>
+        <v>0.497</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3785</v>
+        <v>0.3892</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3761</v>
+        <v>0.4393</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2073</v>
+        <v>0.4826</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3963</v>
+        <v>0.4412</v>
       </c>
     </row>
     <row r="26">
@@ -951,11 +951,11 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
-        <v>0.2038</v>
+        <v>0.2377</v>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="n">
-        <v>0.2077</v>
+        <v>0.2295</v>
       </c>
       <c r="G26" t="n">
         <v>0.2107</v>
@@ -996,20 +996,20 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>0.2208</v>
+        <v>0.2791</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="n">
-        <v>0.2686</v>
+        <v>0.3166</v>
       </c>
       <c r="F28" t="n">
-        <v>0.206</v>
+        <v>0.3527</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2114</v>
+        <v>0.2165</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2439</v>
+        <v>0.3222</v>
       </c>
     </row>
     <row r="29">
@@ -1020,19 +1020,19 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>0.2425</v>
+        <v>0.3726</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2118</v>
+        <v>0.29</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2052</v>
+        <v>0.2155</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2165</v>
+        <v>0.2806</v>
       </c>
       <c r="G29" t="n">
-        <v>0.212</v>
+        <v>0.3098</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1084,7 +1084,7 @@
         <v>0.2223</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2008</v>
+        <v>0.2142</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1103,7 +1103,7 @@
         <v>0.2155</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2012</v>
+        <v>0.2059</v>
       </c>
     </row>
     <row r="34">
@@ -1118,10 +1118,10 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>0.2667</v>
+        <v>0.3664</v>
       </c>
       <c r="H34" t="n">
-        <v>0.2204</v>
+        <v>0.3074</v>
       </c>
     </row>
     <row r="35">
@@ -1134,16 +1134,16 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>0.2067</v>
+        <v>0.5281</v>
       </c>
       <c r="F35" t="n">
-        <v>0.235</v>
+        <v>0.3304</v>
       </c>
       <c r="G35" t="n">
-        <v>0.219</v>
+        <v>0.3828</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2842</v>
+        <v>0.4504</v>
       </c>
     </row>
     <row r="36">
@@ -1154,19 +1154,19 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>0.2158</v>
+        <v>0.4261</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2476</v>
+        <v>0.5111</v>
       </c>
       <c r="E36" t="n">
-        <v>0.2854</v>
+        <v>0.4972</v>
       </c>
       <c r="F36" t="n">
-        <v>0.2143</v>
+        <v>0.4653</v>
       </c>
       <c r="G36" t="n">
-        <v>0.2469</v>
+        <v>0.4712</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1200,7 +1200,7 @@
         <v>0.4395</v>
       </c>
       <c r="E38" t="n">
-        <v>0.2031</v>
+        <v>0.2368</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
@@ -1216,7 +1216,7 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
-        <v>0.2137</v>
+        <v>0.2205</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>0.2175</v>
+        <v>0.2912</v>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="n">
-        <v>0.2017</v>
+        <v>0.203</v>
       </c>
       <c r="G40" t="n">
         <v>0.2552</v>
@@ -1273,13 +1273,13 @@
         <v>0.3148</v>
       </c>
       <c r="D42" t="n">
-        <v>0.2174</v>
+        <v>0.2899</v>
       </c>
       <c r="E42" t="n">
         <v>0.2014</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2405</v>
+        <v>0.2794</v>
       </c>
       <c r="G42" t="n">
         <v>0.2825</v>
@@ -1294,22 +1294,22 @@
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>0.2805</v>
+        <v>0.462</v>
       </c>
       <c r="D43" t="n">
-        <v>0.2633</v>
+        <v>0.4254</v>
       </c>
       <c r="E43" t="n">
-        <v>0.2301</v>
+        <v>0.4057</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2388</v>
+        <v>0.4403</v>
       </c>
       <c r="G43" t="n">
-        <v>0.2499</v>
+        <v>0.459</v>
       </c>
       <c r="H43" t="n">
-        <v>0.3149</v>
+        <v>0.4612</v>
       </c>
     </row>
     <row r="44">
@@ -1335,10 +1335,10 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="n">
-        <v>0.2154</v>
+        <v>0.2731</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2119</v>
+        <v>0.3275</v>
       </c>
       <c r="F45" t="n">
         <v>0.2093</v>
@@ -1355,10 +1355,10 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="n">
-        <v>0.2673</v>
+        <v>0.3013</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2285</v>
+        <v>0.2724</v>
       </c>
       <c r="F46" t="n">
         <v>0.347</v>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>0.2283</v>
+        <v>0.3308</v>
       </c>
       <c r="D47" t="n">
         <v>0.3358</v>
@@ -1387,10 +1387,10 @@
         <v>0.2436</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2295</v>
+        <v>0.2709</v>
       </c>
       <c r="G47" t="n">
-        <v>0.2165</v>
+        <v>0.3557</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
@@ -1416,19 +1416,19 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>0.2008</v>
+        <v>0.2925</v>
       </c>
       <c r="D49" t="n">
-        <v>0.2648</v>
+        <v>0.3675</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2853</v>
+        <v>0.3614</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2597</v>
+        <v>0.3798</v>
       </c>
       <c r="G49" t="n">
-        <v>0.2347</v>
+        <v>0.3423</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -1447,7 +1447,7 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>0.2703</v>
+        <v>0.3381</v>
       </c>
     </row>
     <row r="51">
@@ -1465,10 +1465,10 @@
         <v>0.2111</v>
       </c>
       <c r="F51" t="n">
-        <v>0.2186</v>
+        <v>0.2733</v>
       </c>
       <c r="G51" t="n">
-        <v>0.2072</v>
+        <v>0.3181</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -1480,19 +1480,19 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>0.2452</v>
+        <v>0.3655</v>
       </c>
       <c r="D52" t="n">
-        <v>0.2794</v>
+        <v>0.3492</v>
       </c>
       <c r="E52" t="n">
-        <v>0.2434</v>
+        <v>0.2929</v>
       </c>
       <c r="F52" t="n">
-        <v>0.2784</v>
+        <v>0.3672</v>
       </c>
       <c r="G52" t="n">
-        <v>0.2411</v>
+        <v>0.3846</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -1510,13 +1510,13 @@
         <v>0.3788</v>
       </c>
       <c r="E53" t="n">
-        <v>0.324</v>
+        <v>0.3353</v>
       </c>
       <c r="F53" t="n">
-        <v>0.3372</v>
+        <v>0.3404</v>
       </c>
       <c r="G53" t="n">
-        <v>0.3525</v>
+        <v>0.3936</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -1528,19 +1528,19 @@
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>0.3107</v>
+        <v>0.4573</v>
       </c>
       <c r="D54" t="n">
-        <v>0.2033</v>
+        <v>0.3448</v>
       </c>
       <c r="E54" t="n">
-        <v>0.2415</v>
+        <v>0.4107</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2256</v>
+        <v>0.3721</v>
       </c>
       <c r="G54" t="n">
-        <v>0.2107</v>
+        <v>0.3215</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1552,19 +1552,19 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>0.2185</v>
+        <v>0.2865</v>
       </c>
       <c r="D55" t="n">
-        <v>0.2158</v>
+        <v>0.2763</v>
       </c>
       <c r="E55" t="n">
-        <v>0.2071</v>
+        <v>0.3442</v>
       </c>
       <c r="F55" t="n">
-        <v>0.2118</v>
+        <v>0.2469</v>
       </c>
       <c r="G55" t="n">
-        <v>0.2004</v>
+        <v>0.2629</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -1576,19 +1576,19 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>0.3089</v>
+        <v>0.3902</v>
       </c>
       <c r="D56" t="n">
-        <v>0.2134</v>
+        <v>0.361</v>
       </c>
       <c r="E56" t="n">
-        <v>0.2983</v>
+        <v>0.3768</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3542</v>
+        <v>0.4369</v>
       </c>
       <c r="G56" t="n">
-        <v>0.3461</v>
+        <v>0.4373</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -1600,19 +1600,19 @@
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
-        <v>0.4357</v>
+        <v>0.4996</v>
       </c>
       <c r="D57" t="n">
-        <v>0.4488</v>
+        <v>0.4882</v>
       </c>
       <c r="E57" t="n">
-        <v>0.4616</v>
+        <v>0.5063</v>
       </c>
       <c r="F57" t="n">
-        <v>0.3596</v>
+        <v>0.3973</v>
       </c>
       <c r="G57" t="n">
-        <v>0.3226</v>
+        <v>0.3544</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>0.2857</v>
+        <v>0.3326</v>
       </c>
       <c r="D58" t="n">
         <v>0.3756</v>
@@ -1647,22 +1647,22 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.2796</v>
+        <v>0.4575</v>
       </c>
       <c r="C59" t="n">
-        <v>0.2947</v>
+        <v>0.4499</v>
       </c>
       <c r="D59" t="n">
-        <v>0.3661</v>
+        <v>0.4694</v>
       </c>
       <c r="E59" t="n">
-        <v>0.2793</v>
+        <v>0.4159</v>
       </c>
       <c r="F59" t="n">
-        <v>0.2828</v>
+        <v>0.4126</v>
       </c>
       <c r="G59" t="n">
-        <v>0.2037</v>
+        <v>0.3219</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -1673,22 +1673,22 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.3023</v>
+        <v>0.4226</v>
       </c>
       <c r="C60" t="n">
-        <v>0.4211</v>
+        <v>0.6584</v>
       </c>
       <c r="D60" t="n">
-        <v>0.4034</v>
+        <v>0.5718</v>
       </c>
       <c r="E60" t="n">
-        <v>0.3503</v>
+        <v>0.5129</v>
       </c>
       <c r="F60" t="n">
-        <v>0.2115</v>
+        <v>0.2956</v>
       </c>
       <c r="G60" t="n">
-        <v>0.2268</v>
+        <v>0.2965</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -1699,22 +1699,22 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.2645</v>
+        <v>0.3491</v>
       </c>
       <c r="C61" t="n">
-        <v>0.4216</v>
+        <v>0.6031</v>
       </c>
       <c r="D61" t="n">
-        <v>0.421</v>
+        <v>0.5454</v>
       </c>
       <c r="E61" t="n">
-        <v>0.2622</v>
+        <v>0.3966</v>
       </c>
       <c r="F61" t="n">
-        <v>0.2046</v>
+        <v>0.2461</v>
       </c>
       <c r="G61" t="n">
-        <v>0.2077</v>
+        <v>0.2679</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -1726,16 +1726,16 @@
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>0.2096</v>
+        <v>0.2418</v>
       </c>
       <c r="D62" t="n">
-        <v>0.222</v>
+        <v>0.2714</v>
       </c>
       <c r="E62" t="n">
-        <v>0.2308</v>
+        <v>0.2789</v>
       </c>
       <c r="F62" t="n">
-        <v>0.2096</v>
+        <v>0.241</v>
       </c>
       <c r="G62" t="n">
         <v>0.2549</v>
@@ -1750,10 +1750,10 @@
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>0.2146</v>
+        <v>0.2943</v>
       </c>
       <c r="D63" t="n">
-        <v>0.203</v>
+        <v>0.3154</v>
       </c>
       <c r="E63" t="n">
         <v>0.2278</v>
@@ -1762,7 +1762,7 @@
         <v>0.2614</v>
       </c>
       <c r="G63" t="n">
-        <v>0.2645</v>
+        <v>0.2966</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -1774,13 +1774,13 @@
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>0.2145</v>
+        <v>0.3209</v>
       </c>
       <c r="D64" t="n">
-        <v>0.2159</v>
+        <v>0.2962</v>
       </c>
       <c r="E64" t="n">
-        <v>0.2066</v>
+        <v>0.312</v>
       </c>
       <c r="F64" t="n">
         <v>0.2849</v>
@@ -1835,16 +1835,16 @@
         <v>0.2249</v>
       </c>
       <c r="D67" t="n">
-        <v>0.2292</v>
+        <v>0.2698</v>
       </c>
       <c r="E67" t="n">
-        <v>0.2024</v>
+        <v>0.3248</v>
       </c>
       <c r="F67" t="n">
-        <v>0.2293</v>
+        <v>0.2722</v>
       </c>
       <c r="G67" t="n">
-        <v>0.2024</v>
+        <v>0.2704</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -1856,19 +1856,19 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>0.2137</v>
+        <v>0.3596</v>
       </c>
       <c r="D68" t="n">
-        <v>0.2273</v>
+        <v>0.4412</v>
       </c>
       <c r="E68" t="n">
-        <v>0.2448</v>
+        <v>0.3896</v>
       </c>
       <c r="F68" t="n">
-        <v>0.2614</v>
+        <v>0.5248</v>
       </c>
       <c r="G68" t="n">
-        <v>0.2056</v>
+        <v>0.4124</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -1880,16 +1880,16 @@
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>0.2012</v>
+        <v>0.4053</v>
       </c>
       <c r="D69" t="n">
-        <v>0.2965</v>
+        <v>0.5923</v>
       </c>
       <c r="E69" t="n">
-        <v>0.2324</v>
+        <v>0.4707</v>
       </c>
       <c r="F69" t="n">
-        <v>0.2328</v>
+        <v>0.4729</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
@@ -1902,16 +1902,16 @@
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>0.2731</v>
+        <v>0.4182</v>
       </c>
       <c r="D70" t="n">
-        <v>0.2361</v>
+        <v>0.2542</v>
       </c>
       <c r="E70" t="n">
-        <v>0.2561</v>
+        <v>0.2569</v>
       </c>
       <c r="F70" t="n">
-        <v>0.2506</v>
+        <v>0.3899</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
@@ -1924,22 +1924,22 @@
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>0.2417</v>
+        <v>0.2973</v>
       </c>
       <c r="D71" t="n">
-        <v>0.2144</v>
+        <v>0.3106</v>
       </c>
       <c r="E71" t="n">
-        <v>0.2709</v>
+        <v>0.3808</v>
       </c>
       <c r="F71" t="n">
         <v>0.3342</v>
       </c>
       <c r="G71" t="n">
-        <v>0.2103</v>
+        <v>0.2133</v>
       </c>
       <c r="H71" t="n">
-        <v>0.2501</v>
+        <v>0.3444</v>
       </c>
     </row>
     <row r="72">
@@ -1950,19 +1950,19 @@
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>0.2404</v>
+        <v>0.4277</v>
       </c>
       <c r="D72" t="n">
-        <v>0.2015</v>
+        <v>0.4613</v>
       </c>
       <c r="E72" t="n">
-        <v>0.2343</v>
+        <v>0.4241</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2637</v>
+        <v>0.4373</v>
       </c>
       <c r="G72" t="n">
-        <v>0.2177</v>
+        <v>0.3874</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -1974,19 +1974,19 @@
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
-        <v>0.2124</v>
+        <v>0.3034</v>
       </c>
       <c r="D73" t="n">
-        <v>0.2471</v>
+        <v>0.3453</v>
       </c>
       <c r="E73" t="n">
-        <v>0.2169</v>
+        <v>0.3372</v>
       </c>
       <c r="F73" t="n">
-        <v>0.2839</v>
+        <v>0.3374</v>
       </c>
       <c r="G73" t="n">
-        <v>0.2193</v>
+        <v>0.2739</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -1998,16 +1998,16 @@
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>0.2442</v>
+        <v>0.3036</v>
       </c>
       <c r="D74" t="n">
-        <v>0.2094</v>
+        <v>0.2706</v>
       </c>
       <c r="E74" t="n">
-        <v>0.2176</v>
+        <v>0.3316</v>
       </c>
       <c r="F74" t="n">
-        <v>0.2146</v>
+        <v>0.248</v>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
@@ -2020,19 +2020,19 @@
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>0.3501</v>
+        <v>0.5648</v>
       </c>
       <c r="D75" t="n">
-        <v>0.3368</v>
+        <v>0.6228</v>
       </c>
       <c r="E75" t="n">
-        <v>0.3652</v>
+        <v>0.6505</v>
       </c>
       <c r="F75" t="n">
-        <v>0.3165</v>
+        <v>0.5168</v>
       </c>
       <c r="G75" t="n">
-        <v>0.3092</v>
+        <v>0.5145</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2044,13 +2044,13 @@
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>0.2148</v>
+        <v>0.4308</v>
       </c>
       <c r="D76" t="n">
-        <v>0.2061</v>
+        <v>0.4001</v>
       </c>
       <c r="E76" t="n">
-        <v>0.2105</v>
+        <v>0.4086</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
@@ -2064,16 +2064,16 @@
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>0.2456</v>
+        <v>0.2514</v>
       </c>
       <c r="D77" t="n">
-        <v>0.2682</v>
+        <v>0.287</v>
       </c>
       <c r="E77" t="n">
-        <v>0.2209</v>
+        <v>0.2261</v>
       </c>
       <c r="F77" t="n">
-        <v>0.2025</v>
+        <v>0.2072</v>
       </c>
       <c r="G77" t="n">
         <v>0.2029</v>
@@ -2088,19 +2088,19 @@
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>0.2325</v>
+        <v>0.2474</v>
       </c>
       <c r="D78" t="n">
-        <v>0.2357</v>
+        <v>0.2865</v>
       </c>
       <c r="E78" t="n">
-        <v>0.2016</v>
+        <v>0.2451</v>
       </c>
       <c r="F78" t="n">
-        <v>0.2569</v>
+        <v>0.3238</v>
       </c>
       <c r="G78" t="n">
-        <v>0.2193</v>
+        <v>0.2356</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2126,16 +2126,16 @@
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>0.2449</v>
+        <v>0.546</v>
       </c>
       <c r="D80" t="n">
-        <v>0.2814</v>
+        <v>0.6274</v>
       </c>
       <c r="E80" t="n">
-        <v>0.2588</v>
+        <v>0.552</v>
       </c>
       <c r="F80" t="n">
-        <v>0.2089</v>
+        <v>0.4984</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
@@ -2148,19 +2148,19 @@
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>0.2596</v>
+        <v>0.5063</v>
       </c>
       <c r="D81" t="n">
-        <v>0.2335</v>
+        <v>0.4937</v>
       </c>
       <c r="E81" t="n">
-        <v>0.2302</v>
+        <v>0.5009</v>
       </c>
       <c r="F81" t="n">
-        <v>0.2405</v>
+        <v>0.5392</v>
       </c>
       <c r="G81" t="n">
-        <v>0.2399</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -2178,13 +2178,13 @@
         <v>0.4047</v>
       </c>
       <c r="E82" t="n">
-        <v>0.2077</v>
+        <v>0.4217</v>
       </c>
       <c r="F82" t="n">
         <v>0.3952</v>
       </c>
       <c r="G82" t="n">
-        <v>0.2043</v>
+        <v>0.4556</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -2202,7 +2202,7 @@
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
-        <v>0.2056</v>
+        <v>0.2164</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -2215,7 +2215,7 @@
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="n">
-        <v>0.2242</v>
+        <v>0.2265</v>
       </c>
       <c r="E84" t="n">
         <v>0.2444</v>
@@ -2232,22 +2232,22 @@
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>0.2617</v>
+        <v>0.3048</v>
       </c>
       <c r="D85" t="n">
-        <v>0.2011</v>
+        <v>0.327</v>
       </c>
       <c r="E85" t="n">
-        <v>0.2368</v>
+        <v>0.2777</v>
       </c>
       <c r="F85" t="n">
-        <v>0.202</v>
+        <v>0.2689</v>
       </c>
       <c r="G85" t="n">
-        <v>0.2421</v>
+        <v>0.2799</v>
       </c>
       <c r="H85" t="n">
-        <v>0.2173</v>
+        <v>0.2531</v>
       </c>
     </row>
     <row r="86">
@@ -2257,19 +2257,19 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.2626</v>
+        <v>0.3256</v>
       </c>
       <c r="C86" t="n">
-        <v>0.2822</v>
+        <v>0.3462</v>
       </c>
       <c r="D86" t="n">
-        <v>0.2421</v>
+        <v>0.3628</v>
       </c>
       <c r="E86" t="n">
-        <v>0.2983</v>
+        <v>0.3885</v>
       </c>
       <c r="F86" t="n">
-        <v>0.3273</v>
+        <v>0.4242</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
@@ -2319,13 +2319,13 @@
         <v>0.2259</v>
       </c>
       <c r="F89" t="n">
-        <v>0.2131</v>
+        <v>0.2163</v>
       </c>
       <c r="G89" t="n">
         <v>0.2477</v>
       </c>
       <c r="H89" t="n">
-        <v>0.2157</v>
+        <v>0.238</v>
       </c>
     </row>
     <row r="90">
@@ -2339,13 +2339,13 @@
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="n">
-        <v>0.2357</v>
+        <v>0.4267</v>
       </c>
       <c r="G90" t="n">
-        <v>0.2136</v>
+        <v>0.3631</v>
       </c>
       <c r="H90" t="n">
-        <v>0.2466</v>
+        <v>0.3195</v>
       </c>
     </row>
     <row r="91">
@@ -2356,16 +2356,16 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>0.2111</v>
+        <v>0.3306</v>
       </c>
       <c r="D91" t="n">
-        <v>0.2221</v>
+        <v>0.3021</v>
       </c>
       <c r="E91" t="n">
         <v>0.4119</v>
       </c>
       <c r="F91" t="n">
-        <v>0.2704</v>
+        <v>0.3512</v>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
@@ -2377,19 +2377,19 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.2401</v>
+        <v>0.343</v>
       </c>
       <c r="C92" t="n">
-        <v>0.2008</v>
+        <v>0.2726</v>
       </c>
       <c r="D92" t="n">
-        <v>0.2077</v>
+        <v>0.317</v>
       </c>
       <c r="E92" t="n">
-        <v>0.2006</v>
+        <v>0.4348</v>
       </c>
       <c r="F92" t="n">
-        <v>0.2739</v>
+        <v>0.3675</v>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
@@ -2402,16 +2402,16 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>0.2607</v>
+        <v>0.4019</v>
       </c>
       <c r="D93" t="n">
-        <v>0.2047</v>
+        <v>0.271</v>
       </c>
       <c r="E93" t="n">
-        <v>0.277</v>
+        <v>0.3334</v>
       </c>
       <c r="F93" t="n">
-        <v>0.221</v>
+        <v>0.2879</v>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
@@ -2423,19 +2423,19 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.3701</v>
+        <v>0.493</v>
       </c>
       <c r="C94" t="n">
-        <v>0.2495</v>
+        <v>0.3145</v>
       </c>
       <c r="D94" t="n">
-        <v>0.3119</v>
+        <v>0.3975</v>
       </c>
       <c r="E94" t="n">
-        <v>0.3372</v>
+        <v>0.4812</v>
       </c>
       <c r="F94" t="n">
-        <v>0.2076</v>
+        <v>0.4909</v>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
@@ -2477,7 +2477,7 @@
         <v>0.2072</v>
       </c>
       <c r="F96" t="n">
-        <v>0.2162</v>
+        <v>0.2175</v>
       </c>
       <c r="G96" t="n">
         <v>0.2182</v>
@@ -2522,19 +2522,19 @@
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>0.2159</v>
+        <v>0.4731</v>
       </c>
       <c r="D99" t="n">
         <v>0.4492</v>
       </c>
       <c r="E99" t="n">
-        <v>0.2042</v>
+        <v>0.4108</v>
       </c>
       <c r="F99" t="n">
         <v>0.4812</v>
       </c>
       <c r="G99" t="n">
-        <v>0.4545</v>
+        <v>0.4914</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -2555,7 +2555,7 @@
         <v>0.3054</v>
       </c>
       <c r="F100" t="n">
-        <v>0.2254</v>
+        <v>0.2815</v>
       </c>
       <c r="G100" t="n">
         <v>0.2246</v>
@@ -2570,22 +2570,22 @@
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>0.2357</v>
+        <v>0.5797</v>
       </c>
       <c r="D101" t="n">
-        <v>0.2039</v>
+        <v>0.5014</v>
       </c>
       <c r="E101" t="n">
-        <v>0.2124</v>
+        <v>0.5225</v>
       </c>
       <c r="F101" t="n">
-        <v>0.2079</v>
+        <v>0.4131</v>
       </c>
       <c r="G101" t="n">
-        <v>0.2236</v>
+        <v>0.4833</v>
       </c>
       <c r="H101" t="n">
-        <v>0.2474</v>
+        <v>0.4631</v>
       </c>
     </row>
     <row r="102">
@@ -2615,13 +2615,13 @@
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="n">
-        <v>0.2698</v>
+        <v>0.2873</v>
       </c>
       <c r="E103" t="n">
-        <v>0.2206</v>
+        <v>0.2504</v>
       </c>
       <c r="F103" t="n">
-        <v>0.262</v>
+        <v>0.3494</v>
       </c>
       <c r="G103" t="n">
         <v>0.3096</v>
@@ -2637,10 +2637,10 @@
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="n">
-        <v>0.2708</v>
+        <v>0.317</v>
       </c>
       <c r="E104" t="n">
-        <v>0.2395</v>
+        <v>0.2408</v>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
@@ -2654,19 +2654,19 @@
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
-        <v>0.207</v>
+        <v>0.2459</v>
       </c>
       <c r="D105" t="n">
-        <v>0.2133</v>
+        <v>0.2341</v>
       </c>
       <c r="E105" t="n">
-        <v>0.2591</v>
+        <v>0.3078</v>
       </c>
       <c r="F105" t="n">
-        <v>0.203</v>
+        <v>0.3557</v>
       </c>
       <c r="G105" t="n">
-        <v>0.2192</v>
+        <v>0.3497</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -2677,18 +2677,18 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.2272</v>
+        <v>0.268</v>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="n">
-        <v>0.2086</v>
+        <v>0.3293</v>
       </c>
       <c r="F106" t="n">
-        <v>0.2099</v>
+        <v>0.349</v>
       </c>
       <c r="G106" t="n">
-        <v>0.2087</v>
+        <v>0.2462</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -2722,19 +2722,19 @@
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="n">
-        <v>0.2102</v>
+        <v>0.4583</v>
       </c>
       <c r="D108" t="n">
-        <v>0.2102</v>
+        <v>0.4583</v>
       </c>
       <c r="E108" t="n">
-        <v>0.2311</v>
+        <v>0.4115</v>
       </c>
       <c r="F108" t="n">
         <v>0.2902</v>
       </c>
       <c r="G108" t="n">
-        <v>0.2434</v>
+        <v>0.3571</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -2746,10 +2746,10 @@
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="n">
-        <v>0.2274</v>
+        <v>0.3434</v>
       </c>
       <c r="D109" t="n">
-        <v>0.2129</v>
+        <v>0.3477</v>
       </c>
       <c r="E109" t="n">
         <v>0.2026</v>
@@ -2774,13 +2774,13 @@
         <v>0.2859</v>
       </c>
       <c r="E110" t="n">
-        <v>0.2054</v>
+        <v>0.391</v>
       </c>
       <c r="F110" t="n">
-        <v>0.2364</v>
+        <v>0.3184</v>
       </c>
       <c r="G110" t="n">
-        <v>0.3475</v>
+        <v>0.3515</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.241</v>
+        <v>0.2763</v>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="n">
@@ -2801,10 +2801,10 @@
         <v>0.2142</v>
       </c>
       <c r="F111" t="n">
-        <v>0.3235</v>
+        <v>0.3946</v>
       </c>
       <c r="G111" t="n">
-        <v>0.2234</v>
+        <v>0.3623</v>
       </c>
       <c r="H111" t="inlineStr"/>
     </row>
@@ -2818,13 +2818,13 @@
         <v>0.2405</v>
       </c>
       <c r="C112" t="n">
-        <v>0.2164</v>
+        <v>0.3617</v>
       </c>
       <c r="D112" t="n">
-        <v>0.2083</v>
+        <v>0.2901</v>
       </c>
       <c r="E112" t="n">
-        <v>0.2198</v>
+        <v>0.3673</v>
       </c>
       <c r="F112" t="n">
         <v>0.2411</v>
@@ -2842,16 +2842,16 @@
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
-        <v>0.2095</v>
+        <v>0.3144</v>
       </c>
       <c r="D113" t="n">
-        <v>0.201</v>
+        <v>0.3117</v>
       </c>
       <c r="E113" t="n">
-        <v>0.2083</v>
+        <v>0.3092</v>
       </c>
       <c r="F113" t="n">
-        <v>0.2025</v>
+        <v>0.3474</v>
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
@@ -2902,10 +2902,10 @@
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="n">
-        <v>0.2506</v>
+        <v>0.2971</v>
       </c>
       <c r="D116" t="n">
-        <v>0.2597</v>
+        <v>0.2836</v>
       </c>
       <c r="E116" t="n">
         <v>0.2393</v>
@@ -2926,19 +2926,19 @@
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="n">
-        <v>0.2005</v>
+        <v>0.4366</v>
       </c>
       <c r="D117" t="n">
-        <v>0.2078</v>
+        <v>0.3568</v>
       </c>
       <c r="E117" t="n">
-        <v>0.2395</v>
+        <v>0.3938</v>
       </c>
       <c r="F117" t="n">
-        <v>0.2078</v>
+        <v>0.3774</v>
       </c>
       <c r="G117" t="n">
-        <v>0.2102</v>
+        <v>0.3289</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
@@ -2951,7 +2951,7 @@
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="n">
-        <v>0.2348</v>
+        <v>0.2651</v>
       </c>
       <c r="E118" t="n">
         <v>0.2469</v>
@@ -2973,16 +2973,16 @@
         <v>0.2589</v>
       </c>
       <c r="D119" t="n">
-        <v>0.2073</v>
+        <v>0.2428</v>
       </c>
       <c r="E119" t="n">
         <v>0.3008</v>
       </c>
       <c r="F119" t="n">
-        <v>0.2008</v>
+        <v>0.3808</v>
       </c>
       <c r="G119" t="n">
-        <v>0.202</v>
+        <v>0.2367</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
@@ -2994,16 +2994,16 @@
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="n">
-        <v>0.2901</v>
+        <v>0.3602</v>
       </c>
       <c r="D120" t="n">
-        <v>0.2234</v>
+        <v>0.2586</v>
       </c>
       <c r="E120" t="n">
-        <v>0.3597</v>
+        <v>0.3747</v>
       </c>
       <c r="F120" t="n">
-        <v>0.2245</v>
+        <v>0.4857</v>
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
@@ -3058,7 +3058,7 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="n">
-        <v>0.203</v>
+        <v>0.371</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
@@ -3072,7 +3072,7 @@
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="n">
-        <v>0.5401</v>
+        <v>0.5837</v>
       </c>
       <c r="F124" t="n">
         <v>0.5266</v>
@@ -3140,10 +3140,10 @@
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="n">
-        <v>0.2241</v>
+        <v>0.2477</v>
       </c>
       <c r="D128" t="n">
-        <v>0.2242</v>
+        <v>0.2478</v>
       </c>
       <c r="E128" t="n">
         <v>0.2969</v>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="n">
-        <v>0.2291</v>
+        <v>0.2716</v>
       </c>
       <c r="D131" t="n">
         <v>0.2054</v>
@@ -3258,7 +3258,7 @@
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="n">
-        <v>0.2131</v>
+        <v>0.3838</v>
       </c>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="n">
@@ -3289,7 +3289,7 @@
         <v>0.211</v>
       </c>
       <c r="H135" t="n">
-        <v>0.2258</v>
+        <v>0.2321</v>
       </c>
     </row>
     <row r="136">
@@ -3318,16 +3318,16 @@
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="n">
-        <v>0.2023</v>
+        <v>0.246</v>
       </c>
       <c r="F137" t="n">
-        <v>0.2054</v>
+        <v>0.2453</v>
       </c>
       <c r="G137" t="n">
-        <v>0.2243</v>
+        <v>0.3136</v>
       </c>
       <c r="H137" t="n">
-        <v>0.2498</v>
+        <v>0.3036</v>
       </c>
     </row>
     <row r="138">
@@ -3337,22 +3337,22 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.2173</v>
+        <v>0.4616</v>
       </c>
       <c r="C138" t="n">
-        <v>0.2617</v>
+        <v>0.4537</v>
       </c>
       <c r="D138" t="n">
-        <v>0.305</v>
+        <v>0.482</v>
       </c>
       <c r="E138" t="n">
-        <v>0.2003</v>
+        <v>0.421</v>
       </c>
       <c r="F138" t="n">
-        <v>0.2385</v>
+        <v>0.4135</v>
       </c>
       <c r="G138" t="n">
-        <v>0.2315</v>
+        <v>0.4583</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
@@ -3363,19 +3363,19 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.2129</v>
+        <v>0.3548</v>
       </c>
       <c r="C139" t="n">
-        <v>0.2017</v>
+        <v>0.2233</v>
       </c>
       <c r="D139" t="n">
         <v>0.2371</v>
       </c>
       <c r="E139" t="n">
-        <v>0.2028</v>
+        <v>0.2833</v>
       </c>
       <c r="F139" t="n">
-        <v>0.2891</v>
+        <v>0.306</v>
       </c>
       <c r="G139" t="n">
         <v>0.2069</v>
@@ -3409,16 +3409,16 @@
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="n">
-        <v>0.2578</v>
+        <v>0.3672</v>
       </c>
       <c r="E141" t="n">
         <v>0.266</v>
       </c>
       <c r="F141" t="n">
-        <v>0.2393</v>
+        <v>0.4202</v>
       </c>
       <c r="G141" t="n">
-        <v>0.2249</v>
+        <v>0.4111</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -3429,22 +3429,22 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.207</v>
+        <v>0.6758</v>
       </c>
       <c r="C142" t="n">
-        <v>0.2044</v>
+        <v>0.584</v>
       </c>
       <c r="D142" t="n">
-        <v>0.2304</v>
+        <v>0.7167</v>
       </c>
       <c r="E142" t="n">
-        <v>0.2168</v>
+        <v>0.6101</v>
       </c>
       <c r="F142" t="n">
-        <v>0.2067</v>
+        <v>0.496</v>
       </c>
       <c r="G142" t="n">
-        <v>0.2029</v>
+        <v>0.7386</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -3458,16 +3458,16 @@
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="n">
-        <v>0.2026</v>
+        <v>0.5167</v>
       </c>
       <c r="F143" t="n">
-        <v>0.2007</v>
+        <v>0.5382</v>
       </c>
       <c r="G143" t="n">
-        <v>0.2169</v>
+        <v>0.5461</v>
       </c>
       <c r="H143" t="n">
-        <v>0.2287</v>
+        <v>0.5317</v>
       </c>
     </row>
     <row r="144">
@@ -3479,7 +3479,7 @@
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="n">
-        <v>0.2006</v>
+        <v>0.5111</v>
       </c>
       <c r="E144" t="n">
         <v>0.4568</v>
@@ -3505,7 +3505,7 @@
         <v>0.2164</v>
       </c>
       <c r="F145" t="n">
-        <v>0.2061</v>
+        <v>0.2324</v>
       </c>
       <c r="G145" t="n">
         <v>0.2273</v>
@@ -3521,16 +3521,16 @@
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="n">
-        <v>0.2383</v>
+        <v>0.2536</v>
       </c>
       <c r="E146" t="n">
-        <v>0.2887</v>
+        <v>0.3073</v>
       </c>
       <c r="F146" t="n">
-        <v>0.2852</v>
+        <v>0.3035</v>
       </c>
       <c r="G146" t="n">
-        <v>0.242</v>
+        <v>0.2575</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
@@ -3546,10 +3546,10 @@
         <v>0.2763</v>
       </c>
       <c r="E147" t="n">
-        <v>0.2254</v>
+        <v>0.3647</v>
       </c>
       <c r="F147" t="n">
-        <v>0.2154</v>
+        <v>0.2732</v>
       </c>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr"/>
@@ -3562,16 +3562,16 @@
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="n">
-        <v>0.2123</v>
+        <v>0.2899</v>
       </c>
       <c r="D148" t="n">
-        <v>0.2109</v>
+        <v>0.2608</v>
       </c>
       <c r="E148" t="n">
-        <v>0.2544</v>
+        <v>0.4323</v>
       </c>
       <c r="F148" t="n">
-        <v>0.2125</v>
+        <v>0.2575</v>
       </c>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr"/>
